--- a/static/standards-correlations/Florida_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Florida_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$27</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Grades 9-12, 8 strands - scored at STANDARD level, benchmarks not available</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Grades 9-12, 8 strands - scored at STANDARD level, benchmarks not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -698,7 +699,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Defending collaboration - arguing for it, not merely doing it - is met at the Discovery tier and in Extensions rather than in the C and Python core. Discovery Systems 3 runs a two-round exercise in which one round forbids mid-task correction, then asks what that cost, which is an argument for coordination built from evidence the student generated. Ext 3.3B has partners trade libraries and report what made them usable. No core lab requires a student to justify the collaborative approach itself.</t>
+          <t>Defending collaboration - arguing for it, not merely doing it - is met at the Introductory tier and in Extensions rather than in the C and Python core. Introductory Systems 3 runs a two-round exercise in which one round forbids mid-task correction, then asks what that cost, which is an argument for coordination built from evidence the student generated. Ext 3.3B has partners trade libraries and report what made them usable. No core lab requires a student to justify the collaborative approach itself.</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1136,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app routing a driver into a wall, Unit 1.4 through a delivery app whose stored model has drifted from reality. Ext 5.2D (Should It Exist?) requires researching a real incident involving a deployed system and defending a position on whether it should exist, and Ext 5.3D (Who's Left Out?) asks who a technology excludes. Discovery Systems 12 asks whose responsibility it is to anticipate harm from a genuinely useful invention. Assessment, not just description.</t>
+          <t>Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app routing a driver into a wall, Unit 1.4 through a delivery app whose stored model has drifted from reality. Ext 5.2D (Should It Exist?) requires researching a real incident involving a deployed system and defending a position on whether it should exist, and Ext 5.3D (Who's Left Out?) asks who a technology excludes. Introductory Systems 12 asks whose responsibility it is to anticipate harm from a genuinely useful invention. Assessment, not just description.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1405,7 @@
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>NOT ADDRESSED. Social engineering, phishing, pretexting, and their consequences appear nowhere in either track or in the Discovery projects. No adjacent evidence to cite.</t>
+          <t>NOT ADDRESSED. Social engineering, phishing, pretexting, and their consequences appear nowhere in either track or in the Introductory projects. No adjacent evidence to cite.</t>
         </is>
       </c>
     </row>
@@ -1519,6 +1520,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1563,7 +1565,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1577,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1711,6 +1713,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
 MANDATE CONTEXT: Florida does not require a computer science credit for high school graduation. Under Florida statute a computer science course may satisfy certain mathematics or science graduation requirements, which is the practical route into a Florida master schedule. Verify the current course-code equivalency list with FLDOE before advising a district.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT: 10 Full, 6 Partial, 7 blank of 23. Read BY STRAND - the aggregate is misleading here because two strands are outside any CS curriculum's normal scope.
   Emerging Technologies          3 Full of 3            - includes the robotics standard
